--- a/api-test2/all_result/ALL_RESULT_SESSIONpawapo.xlsx
+++ b/api-test2/all_result/ALL_RESULT_SESSIONpawapo.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11116"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DDCAA48-E7D3-FA45-B921-14164D524B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0726A6D4-79BC-5642-915C-64F89CAD524F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15420" yWindow="500" windowWidth="13380" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13340" yWindow="500" windowWidth="15420" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Session_6" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -522,22 +522,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>-0.94724788360273438</c:v>
+                  <c:v>1.1078417094005921E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7936343759835107</c:v>
+                  <c:v>3.5715038291901293</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8593497124856548</c:v>
+                  <c:v>2.6043215975888097</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.7566756879271397</c:v>
+                  <c:v>7.8718665511494077</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.5614003885983099</c:v>
+                  <c:v>8.5265170706829743</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.8681682842264316</c:v>
+                  <c:v>10.050843843260406</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1586,10 +1586,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:AA92"/>
+  <dimension ref="A2:AK92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:37">
       <c r="A2">
         <v>12</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>14</v>
       </c>
       <c r="J2" cm="1">
-        <f t="array" ref="J2:O2">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I2))</f>
+        <f t="array" ref="J2:P2">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I2))</f>
         <v>3.9854211929010432</v>
       </c>
       <c r="K2">
@@ -1636,8 +1636,11 @@
       <c r="O2">
         <v>3.5105441433566398</v>
       </c>
-    </row>
-    <row r="3" spans="1:27">
+      <c r="P2">
+        <v>3.9849514404368733</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3">
         <v>12</v>
       </c>
@@ -1666,7 +1669,7 @@
         <v>15</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3:L3">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I3))</f>
+        <f t="array" ref="J3:N3">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I3))</f>
         <v>4.2104111986001698</v>
       </c>
       <c r="K3">
@@ -1675,8 +1678,14 @@
       <c r="L3" s="1">
         <v>-2.6549399999999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="M3">
+        <v>-0.15473488755931442</v>
+      </c>
+      <c r="N3">
+        <v>6.5022288414133129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
       <c r="A4">
         <v>12</v>
       </c>
@@ -1705,7 +1714,7 @@
         <v>36</v>
       </c>
       <c r="J4" cm="1">
-        <f t="array" ref="J4:M4">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I4))</f>
+        <f t="array" ref="J4:O4">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I4))</f>
         <v>6.1521905857539991</v>
       </c>
       <c r="K4">
@@ -1715,10 +1724,16 @@
         <v>7.5056503779908041</v>
       </c>
       <c r="M4">
-        <v>3.4797501741943364</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
+        <v>1.8848585674743106</v>
+      </c>
+      <c r="N4">
+        <v>8.8260240091693305</v>
+      </c>
+      <c r="O4">
+        <v>1.9901513162642743</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
       <c r="A5">
         <v>12</v>
       </c>
@@ -1751,7 +1766,7 @@
         <v>-5.1045861297539261</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:37">
       <c r="A6">
         <v>12</v>
       </c>
@@ -1793,7 +1808,7 @@
         <v>3.0769422576853174</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:37">
       <c r="I7" t="s">
         <v>18</v>
       </c>
@@ -1805,7 +1820,7 @@
         <v>20.83978466257669</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:37">
       <c r="A8">
         <v>12</v>
       </c>
@@ -1834,14 +1849,20 @@
         <v>35</v>
       </c>
       <c r="J8" cm="1">
-        <f t="array" ref="J8:K8">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I8))</f>
+        <f t="array" ref="J8:M8">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I8))</f>
         <v>-0.39742</v>
       </c>
       <c r="K8">
         <v>1.0468889271436979</v>
       </c>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="L8">
+        <v>0.87745608128787467</v>
+      </c>
+      <c r="M8">
+        <v>1.6601286605501144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
       <c r="A9">
         <v>12</v>
       </c>
@@ -1870,7 +1891,7 @@
         <v>19</v>
       </c>
       <c r="J9" cm="1">
-        <f t="array" ref="J9:N9">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I9))</f>
+        <f t="array" ref="J9:O9">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I9))</f>
         <v>0.83379899999999996</v>
       </c>
       <c r="K9">
@@ -1883,10 +1904,13 @@
         <v>2.0071221313637579</v>
       </c>
       <c r="N9">
-        <v>-7.0940100078678228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27">
+        <v>2.9241015778040946E-2</v>
+      </c>
+      <c r="O9">
+        <v>-6.1903869022801388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
       <c r="A10">
         <v>12</v>
       </c>
@@ -1915,7 +1939,7 @@
         <v>20</v>
       </c>
       <c r="J10" cm="1">
-        <f t="array" ref="J10:L10">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I10))</f>
+        <f t="array" ref="J10:M10">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I10))</f>
         <v>10.476760000000001</v>
       </c>
       <c r="K10">
@@ -1924,8 +1948,11 @@
       <c r="L10">
         <v>-3.1141337386018222</v>
       </c>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="M10">
+        <v>5.1434042232087904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1954,7 +1981,7 @@
         <v>21</v>
       </c>
       <c r="J11" cm="1">
-        <f t="array" ref="J11:O11">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I11))</f>
+        <f t="array" ref="J11:R11">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I11))</f>
         <v>30.069172618301806</v>
       </c>
       <c r="K11">
@@ -1972,8 +1999,17 @@
       <c r="O11">
         <v>17.47812831389183</v>
       </c>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="P11">
+        <v>-0.95181321735718427</v>
+      </c>
+      <c r="Q11">
+        <v>10.570664824427098</v>
+      </c>
+      <c r="R11">
+        <v>17.693460430059801</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -2009,7 +2045,7 @@
         <v>5.5519410000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:37">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -2038,17 +2074,23 @@
         <v>23</v>
       </c>
       <c r="J13" cm="1">
-        <f t="array" ref="J13:L13">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I13))</f>
+        <f t="array" ref="J13:N13">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I13))</f>
         <v>2.5801265458728722</v>
       </c>
       <c r="K13">
         <v>-4.4288100000000004</v>
       </c>
       <c r="L13">
-        <v>12.015201578947384</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
+        <v>24.193745225362875</v>
+      </c>
+      <c r="M13">
+        <v>11.998200992555837</v>
+      </c>
+      <c r="N13">
+        <v>14.938304728867635</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -2084,7 +2126,7 @@
         <v>9.1245980000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:37">
       <c r="A15" s="1">
         <v>10</v>
       </c>
@@ -2113,14 +2155,20 @@
         <v>25</v>
       </c>
       <c r="J15" cm="1">
-        <f t="array" ref="J15:K15">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I15))</f>
+        <f t="array" ref="J15:M15">TRANSPOSE(_xlfn._xlws.FILTER(F:F, C:C=I15))</f>
         <v>3.0802488648772908</v>
       </c>
       <c r="K15">
         <v>7.7963310000000003</v>
       </c>
-    </row>
-    <row r="16" spans="1:27">
+      <c r="L15">
+        <v>7.4132739099012213</v>
+      </c>
+      <c r="M15">
+        <v>14.213108443578548</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
       <c r="A16" s="1">
         <v>10</v>
       </c>
@@ -2149,7 +2197,7 @@
         <v>29</v>
       </c>
       <c r="J16" cm="1">
-        <f t="array" ref="J16:AA16">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I16))</f>
+        <f t="array" ref="J16:AK16">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I16))</f>
         <v>-11.82088744588745</v>
       </c>
       <c r="K16">
@@ -2201,10 +2249,40 @@
         <v>8.6928187633262297</v>
       </c>
       <c r="AA16">
+        <v>5.3841071336291435</v>
+      </c>
+      <c r="AB16">
+        <v>3.9849514404368733</v>
+      </c>
+      <c r="AC16">
+        <v>-0.95181321735718427</v>
+      </c>
+      <c r="AD16">
+        <v>0.79779908404995581</v>
+      </c>
+      <c r="AE16">
+        <v>7.4132739099012213</v>
+      </c>
+      <c r="AF16">
+        <v>-0.15473488755931442</v>
+      </c>
+      <c r="AG16">
+        <v>10.570664824427098</v>
+      </c>
+      <c r="AH16">
+        <v>4.0248887866237055</v>
+      </c>
+      <c r="AI16">
+        <v>-20.210708332083428</v>
+      </c>
+      <c r="AJ16">
+        <v>6.5022288414133129</v>
+      </c>
+      <c r="AK16">
         <v>-7.0823785826771655</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:24">
       <c r="A17" s="1">
         <v>10</v>
       </c>
@@ -2233,7 +2311,7 @@
         <v>32</v>
       </c>
       <c r="J17" cm="1">
-        <f t="array" ref="J17:O17">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I17))</f>
+        <f t="array" ref="J17:S17">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I17))</f>
         <v>3.0802488648772908</v>
       </c>
       <c r="K17">
@@ -2249,10 +2327,22 @@
         <v>1.6833630421865706</v>
       </c>
       <c r="O17">
+        <v>2.9241015778040946E-2</v>
+      </c>
+      <c r="P17">
+        <v>1.8848585674743106</v>
+      </c>
+      <c r="Q17">
+        <v>14.213108443578548</v>
+      </c>
+      <c r="R17">
+        <v>8.8260240091693305</v>
+      </c>
+      <c r="S17">
         <v>5.1430853488372037</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:24">
       <c r="A18" s="1">
         <v>10</v>
       </c>
@@ -2281,7 +2371,7 @@
         <v>33</v>
       </c>
       <c r="J18" cm="1">
-        <f t="array" ref="J18:N18">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I18))</f>
+        <f t="array" ref="J18:P18">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I18))</f>
         <v>4.2104111986001698</v>
       </c>
       <c r="K18">
@@ -2296,8 +2386,14 @@
       <c r="N18">
         <v>17.47812831389183</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="O18">
+        <v>8.6262269883503535</v>
+      </c>
+      <c r="P18">
+        <v>17.693460430059801</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
       <c r="A19" s="1">
         <v>10</v>
       </c>
@@ -2326,7 +2422,7 @@
         <v>34</v>
       </c>
       <c r="J19" cm="1">
-        <f t="array" ref="J19:O19">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I19))</f>
+        <f t="array" ref="J19:P19">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I19))</f>
         <v>7.7963310000000003</v>
       </c>
       <c r="K19">
@@ -2339,13 +2435,16 @@
         <v>-3.1141337386018222</v>
       </c>
       <c r="N19">
-        <v>-7.0940100078678228</v>
+        <v>1.6601286605501144</v>
       </c>
       <c r="O19">
-        <v>3.4797501741943364</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>-6.1903869022801388</v>
+      </c>
+      <c r="P19">
+        <v>1.9901513162642743</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
       <c r="A20" s="1">
         <v>8</v>
       </c>
@@ -2374,7 +2473,7 @@
         <v>27</v>
       </c>
       <c r="J20" cm="1">
-        <f t="array" ref="J20:T20">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I20))</f>
+        <f t="array" ref="J20:X20">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I20))</f>
         <v>3.9854211929010432</v>
       </c>
       <c r="K20">
@@ -2405,10 +2504,22 @@
         <v>3.5105441433566398</v>
       </c>
       <c r="T20">
+        <v>5.1434042232087904</v>
+      </c>
+      <c r="U20">
+        <v>0.87745608128787467</v>
+      </c>
+      <c r="V20">
+        <v>24.193745225362875</v>
+      </c>
+      <c r="W20">
+        <v>11.998200992555837</v>
+      </c>
+      <c r="X20">
         <v>20.83978466257669</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:24">
       <c r="A21" s="1">
         <v>8</v>
       </c>
@@ -2437,7 +2548,7 @@
         <v>26</v>
       </c>
       <c r="J21" cm="1">
-        <f t="array" ref="J21:M21">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I21))</f>
+        <f t="array" ref="J21:N21">TRANSPOSE(_xlfn._xlws.FILTER(F:F, H:H=I21))</f>
         <v>6.1521905857539991</v>
       </c>
       <c r="K21">
@@ -2447,19 +2558,22 @@
         <v>-1.0463886103081421</v>
       </c>
       <c r="M21">
-        <v>12.015201578947384</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>13.463880649101384</v>
+      </c>
+      <c r="N21">
+        <v>14.938304728867635</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
       <c r="I22" t="s">
         <v>29</v>
       </c>
       <c r="J22" cm="1">
         <f t="array" ref="J22">AVERAGE(_xlfn._xlws.FILTER(F:F, H:H=I16))</f>
-        <v>-0.94724788360273438</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>1.1078417094005921E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
       <c r="A23" s="1">
         <v>8</v>
       </c>
@@ -2489,19 +2603,19 @@
       </c>
       <c r="J23" cm="1">
         <f t="array" ref="J23">AVERAGE(_xlfn._xlws.FILTER(F:F, H:H=I23))</f>
-        <v>1.7936343759835107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>3.5715038291901293</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
       <c r="I24" t="s">
         <v>49</v>
       </c>
       <c r="J24" cm="1">
         <f t="array" ref="J24">AVERAGE(_xlfn._xlws.FILTER(F:F, H:H=I24))</f>
-        <v>2.8593497124856548</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>2.6043215975888097</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
       <c r="A25" s="1">
         <v>8</v>
       </c>
@@ -2531,10 +2645,10 @@
       </c>
       <c r="J25" cm="1">
         <f t="array" ref="J25">AVERAGE(_xlfn._xlws.FILTER(F:F, H:H=I25))</f>
-        <v>5.7566756879271397</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>7.8718665511494077</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
       <c r="A26" s="1">
         <v>8</v>
       </c>
@@ -2564,10 +2678,10 @@
       </c>
       <c r="J26" cm="1">
         <f t="array" ref="J26">AVERAGE(_xlfn._xlws.FILTER(F:F, H:H=I26))</f>
-        <v>6.5614003885983099</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <v>8.5265170706829743</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24">
       <c r="A27" s="1">
         <v>2</v>
       </c>
@@ -2597,19 +2711,19 @@
       </c>
       <c r="J27" cm="1">
         <f t="array" ref="J27">AVERAGE(_xlfn._xlws.FILTER(F:F, H:H=I27))</f>
-        <v>9.8681682842264316</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <v>10.050843843260406</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24">
       <c r="I28" t="s">
         <v>57</v>
       </c>
       <c r="J28" cm="1">
         <f t="array" ref="J28">AVERAGE(_xlfn._xlws.FILTER(F:F, H:H=I28))</f>
-        <v>15.110055478502076</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>8.4033346181907902</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
       <c r="A29" s="1">
         <v>2</v>
       </c>
@@ -2639,10 +2753,10 @@
       </c>
       <c r="J29" cm="1">
         <f t="array" ref="J29">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I29))</f>
-        <v>89.104794876707956</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>88.183085635561</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
       <c r="A30" s="1">
         <v>2</v>
       </c>
@@ -2672,10 +2786,10 @@
       </c>
       <c r="J30" cm="1">
         <f t="array" ref="J30">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I30))</f>
-        <v>85.540761452318463</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <v>83.800201146200237</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24">
       <c r="A31" s="1">
         <v>2</v>
       </c>
@@ -2705,10 +2819,10 @@
       </c>
       <c r="J31" cm="1">
         <f t="array" ref="J31">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I31))</f>
-        <v>70.350639825805658</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <v>71.84023868373572</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24">
       <c r="A32" s="1">
         <v>2</v>
       </c>
@@ -2837,7 +2951,7 @@
       </c>
       <c r="J35" cm="1">
         <f t="array" ref="J35">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I35))</f>
-        <v>80.458330191082808</v>
+        <v>79.853599484681681</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2870,7 +2984,7 @@
       </c>
       <c r="J36" cm="1">
         <f t="array" ref="J36">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I36))</f>
-        <v>79.035122330659533</v>
+        <v>78.131499225071835</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2879,7 +2993,7 @@
       </c>
       <c r="J37" cm="1">
         <f t="array" ref="J37">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I37))</f>
-        <v>74.829236421356427</v>
+        <v>74.327525771615768</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2912,7 +3026,7 @@
       </c>
       <c r="J38" cm="1">
         <f t="array" ref="J38">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I38))</f>
-        <v>85.694813340234646</v>
+        <v>82.450350840452302</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2978,7 +3092,7 @@
       </c>
       <c r="J40" cm="1">
         <f t="array" ref="J40">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I40))</f>
-        <v>76.723668421052622</v>
+        <v>73.800565271132371</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -3044,7 +3158,7 @@
       </c>
       <c r="J42" cm="1">
         <f t="array" ref="J42">AVERAGE(_xlfn._xlws.FILTER(D:D, C:C=I42))</f>
-        <v>84.277330275590543</v>
+        <v>97.045837510876737</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -3227,7 +3341,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>3</v>
       </c>
@@ -3253,7 +3367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>3</v>
       </c>
@@ -3279,7 +3393,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>3</v>
       </c>
@@ -3305,602 +3419,602 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
-      <c r="I52">
+    <row r="52" spans="1:8">
+      <c r="A52">
         <v>9</v>
       </c>
-      <c r="J52">
+      <c r="B52">
         <v>1</v>
       </c>
-      <c r="K52" t="s">
+      <c r="C52" t="s">
         <v>8</v>
       </c>
-      <c r="L52">
+      <c r="D52">
         <v>72.822393822393806</v>
       </c>
-      <c r="M52">
+      <c r="E52">
         <v>77.965798045602611</v>
       </c>
-      <c r="N52">
+      <c r="F52">
         <v>5.1434042232087904</v>
       </c>
-      <c r="O52">
+      <c r="G52">
         <v>614</v>
       </c>
-      <c r="P52" t="s">
+      <c r="H52" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
-      <c r="I53">
+    <row r="53" spans="1:8">
+      <c r="A53">
         <v>9</v>
       </c>
-      <c r="J53">
+      <c r="B53">
         <v>2</v>
       </c>
-      <c r="K53" t="s">
+      <c r="C53" t="s">
         <v>7</v>
       </c>
-      <c r="L53">
+      <c r="D53">
         <v>74.517006802721085</v>
       </c>
-      <c r="M53">
+      <c r="E53">
         <v>74.546247818499126</v>
       </c>
-      <c r="N53">
+      <c r="F53">
         <v>2.9241015778040946E-2</v>
       </c>
-      <c r="O53">
+      <c r="G53">
         <v>573</v>
       </c>
-      <c r="P53" t="s">
+      <c r="H53" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
-      <c r="I54">
+    <row r="54" spans="1:8">
+      <c r="A54">
         <v>9</v>
       </c>
-      <c r="J54">
+      <c r="B54">
         <v>3</v>
       </c>
-      <c r="K54" t="s">
+      <c r="C54" t="s">
         <v>50</v>
       </c>
-      <c r="L54">
+      <c r="D54">
         <v>72.822393822393806</v>
       </c>
-      <c r="M54">
+      <c r="E54">
         <v>78.20650095602295</v>
       </c>
-      <c r="N54">
-        <f>M54-L54</f>
+      <c r="F54">
+        <f>E54-D54</f>
         <v>5.3841071336291435</v>
       </c>
-      <c r="O54">
+      <c r="G54">
         <v>523</v>
       </c>
-      <c r="P54" t="s">
+      <c r="H54" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
-      <c r="I55">
+    <row r="55" spans="1:8">
+      <c r="A55">
         <v>9</v>
       </c>
-      <c r="J55">
+      <c r="B55">
         <v>4</v>
       </c>
-      <c r="K55" t="s">
+      <c r="C55" t="s">
         <v>0</v>
       </c>
-      <c r="L55">
+      <c r="D55">
         <v>82.652830188679246</v>
       </c>
-      <c r="M55">
+      <c r="E55">
         <v>86.63778162911612</v>
       </c>
-      <c r="N55">
+      <c r="F55">
         <v>3.9849514404368733</v>
       </c>
-      <c r="O55">
+      <c r="G55">
         <v>577</v>
       </c>
-      <c r="P55" t="s">
+      <c r="H55" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
-      <c r="I56">
+    <row r="56" spans="1:8">
+      <c r="A56">
         <v>9</v>
       </c>
-      <c r="J56">
+      <c r="B56">
         <v>5</v>
       </c>
-      <c r="K56" t="s">
+      <c r="C56" t="s">
         <v>9</v>
       </c>
-      <c r="L56">
+      <c r="D56">
         <v>77.833962264150941</v>
       </c>
-      <c r="M56">
+      <c r="E56">
         <v>76.882149046793756</v>
       </c>
-      <c r="N56">
+      <c r="F56">
         <v>-0.95181321735718427</v>
       </c>
-      <c r="O56">
+      <c r="G56">
         <v>577</v>
       </c>
-      <c r="P56" t="s">
+      <c r="H56" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
-      <c r="I57">
+    <row r="57" spans="1:8">
+      <c r="A57">
         <v>16</v>
       </c>
-      <c r="J57">
+      <c r="B57">
         <v>1</v>
       </c>
-      <c r="K57" t="s">
+      <c r="C57" t="s">
         <v>52</v>
       </c>
-      <c r="L57">
+      <c r="D57">
         <v>84.796019900497512</v>
       </c>
-      <c r="M57">
+      <c r="E57">
         <v>85.593818984547468</v>
       </c>
-      <c r="N57">
+      <c r="F57">
         <v>0.79779908404995581</v>
       </c>
-      <c r="O57">
+      <c r="G57">
         <v>453</v>
       </c>
-      <c r="P57" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
-      <c r="I58">
+    <row r="58" spans="1:8">
+      <c r="A58">
         <v>16</v>
       </c>
-      <c r="J58">
+      <c r="B58">
         <v>2</v>
       </c>
-      <c r="K58" t="s">
+      <c r="C58" t="s">
         <v>35</v>
       </c>
-      <c r="L58">
+      <c r="D58">
         <v>81.529411764705884</v>
       </c>
-      <c r="M58">
+      <c r="E58">
         <v>82.406867845993759</v>
       </c>
-      <c r="N58">
+      <c r="F58">
         <v>0.87745608128787467</v>
       </c>
-      <c r="O58">
+      <c r="G58">
         <v>961</v>
       </c>
-      <c r="P58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
-      <c r="I59">
+    <row r="59" spans="1:8">
+      <c r="A59">
         <v>16</v>
       </c>
-      <c r="J59">
+      <c r="B59">
         <v>5</v>
       </c>
-      <c r="K59" t="s">
+      <c r="C59" t="s">
         <v>11</v>
       </c>
-      <c r="L59">
+      <c r="D59">
         <v>70.846590909090907</v>
       </c>
-      <c r="M59">
+      <c r="E59">
         <v>95.040336134453781</v>
       </c>
-      <c r="N59">
+      <c r="F59">
         <v>24.193745225362875</v>
       </c>
-      <c r="O59">
+      <c r="G59">
         <v>1190</v>
       </c>
-      <c r="P59" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
-      <c r="I60">
+    <row r="60" spans="1:8">
+      <c r="A60">
         <v>16</v>
       </c>
-      <c r="J60">
+      <c r="B60">
         <v>6</v>
       </c>
-      <c r="K60" t="s">
+      <c r="C60" t="s">
         <v>13</v>
       </c>
-      <c r="L60">
+      <c r="D60">
         <v>111.28571428571429</v>
       </c>
-      <c r="M60">
+      <c r="E60">
         <v>118.69898819561551</v>
       </c>
-      <c r="N60">
+      <c r="F60">
         <v>7.4132739099012213</v>
       </c>
-      <c r="O60">
+      <c r="G60">
         <v>1186</v>
       </c>
-      <c r="P60" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
-      <c r="I61">
+    <row r="61" spans="1:8">
+      <c r="A61">
         <v>16</v>
       </c>
-      <c r="J61">
+      <c r="B61">
         <v>7</v>
       </c>
-      <c r="K61" t="s">
+      <c r="C61" t="s">
         <v>1</v>
       </c>
-      <c r="L61">
+      <c r="D61">
         <v>83.391221374045799</v>
       </c>
-      <c r="M61">
+      <c r="E61">
         <v>83.236486486486484</v>
       </c>
-      <c r="N61">
+      <c r="F61">
         <v>-0.15473488755931442</v>
       </c>
-      <c r="O61">
+      <c r="G61">
         <v>888</v>
       </c>
-      <c r="P61" s="1" t="s">
+      <c r="H61" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
-      <c r="I62">
+    <row r="62" spans="1:8">
+      <c r="A62">
         <v>16</v>
       </c>
-      <c r="J62">
+      <c r="B62">
         <v>8</v>
       </c>
-      <c r="K62" t="s">
+      <c r="C62" t="s">
         <v>53</v>
       </c>
-      <c r="L62">
+      <c r="D62">
         <v>66.750611246943762</v>
       </c>
-      <c r="M62">
+      <c r="E62">
         <v>75.376838235294116</v>
       </c>
-      <c r="N62">
+      <c r="F62">
         <v>8.6262269883503535</v>
       </c>
-      <c r="O62">
+      <c r="G62">
         <v>544</v>
       </c>
-      <c r="P62" s="1" t="s">
+      <c r="H62" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
-      <c r="I63">
+    <row r="63" spans="1:8">
+      <c r="A63">
         <v>16</v>
       </c>
-      <c r="J63">
+      <c r="B63">
         <v>9</v>
       </c>
-      <c r="K63" t="s">
+      <c r="C63" t="s">
         <v>9</v>
       </c>
-      <c r="L63">
+      <c r="D63">
         <v>76.60928961748634</v>
       </c>
-      <c r="M63">
+      <c r="E63">
         <v>87.179954441913438</v>
       </c>
-      <c r="N63">
+      <c r="F63">
         <v>10.570664824427098</v>
       </c>
-      <c r="O63">
+      <c r="G63">
         <v>878</v>
       </c>
-      <c r="P63" s="1" t="s">
+      <c r="H63" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
-      <c r="I64">
+    <row r="64" spans="1:8">
+      <c r="A64">
         <v>16</v>
       </c>
-      <c r="J64">
+      <c r="B64">
         <v>10</v>
       </c>
-      <c r="K64" t="s">
+      <c r="C64" t="s">
         <v>2</v>
       </c>
-      <c r="L64">
+      <c r="D64">
         <v>77.909604519774007</v>
       </c>
-      <c r="M64">
+      <c r="E64">
         <v>79.794463087248317</v>
       </c>
-      <c r="N64">
+      <c r="F64">
         <v>1.8848585674743106</v>
       </c>
-      <c r="O64">
+      <c r="G64">
         <v>1192</v>
       </c>
-      <c r="P64" s="1" t="s">
+      <c r="H64" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="65" spans="9:16">
-      <c r="I65">
+    <row r="65" spans="1:8">
+      <c r="A65">
         <v>15</v>
       </c>
-      <c r="J65">
+      <c r="B65">
         <v>1</v>
       </c>
-      <c r="K65" t="s">
+      <c r="C65" t="s">
         <v>52</v>
       </c>
-      <c r="L65">
+      <c r="D65">
         <v>78.954545454545453</v>
       </c>
-      <c r="M65">
+      <c r="E65">
         <v>92.418426103646837</v>
       </c>
-      <c r="N65">
+      <c r="F65">
         <v>13.463880649101384</v>
       </c>
-      <c r="O65">
+      <c r="G65">
         <v>521</v>
       </c>
-      <c r="P65" s="1" t="s">
+      <c r="H65" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="9:16">
-      <c r="I66">
+    <row r="66" spans="1:8">
+      <c r="A66">
         <v>15</v>
       </c>
-      <c r="J66">
+      <c r="B66">
         <v>2</v>
       </c>
-      <c r="K66" t="s">
+      <c r="C66" t="s">
         <v>35</v>
       </c>
-      <c r="L66">
+      <c r="D66">
         <v>76.968325791855207</v>
       </c>
-      <c r="M66">
+      <c r="E66">
         <v>78.628454452405322</v>
       </c>
-      <c r="N66">
+      <c r="F66">
         <v>1.6601286605501144</v>
       </c>
-      <c r="O66">
+      <c r="G66">
         <v>977</v>
       </c>
-      <c r="P66" s="1" t="s">
+      <c r="H66" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="67" spans="9:16">
-      <c r="I67">
+    <row r="67" spans="1:8">
+      <c r="A67">
         <v>15</v>
       </c>
-      <c r="J67">
+      <c r="B67">
         <v>3</v>
       </c>
-      <c r="K67" t="s">
+      <c r="C67" t="s">
         <v>54</v>
       </c>
-      <c r="L67">
+      <c r="D67">
         <v>84.966981132075475</v>
       </c>
-      <c r="M67">
+      <c r="E67">
         <v>88.99186991869918</v>
       </c>
-      <c r="N67">
+      <c r="F67">
         <v>4.0248887866237055</v>
       </c>
-      <c r="O67">
+      <c r="G67">
         <v>738</v>
       </c>
-      <c r="P67" s="1" t="s">
+      <c r="H67" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="68" spans="9:16">
-      <c r="I68">
+    <row r="68" spans="1:8">
+      <c r="A68">
         <v>15</v>
       </c>
-      <c r="J68">
+      <c r="B68">
         <v>4</v>
       </c>
-      <c r="K68" t="s">
+      <c r="C68" t="s">
         <v>55</v>
       </c>
-      <c r="L68">
+      <c r="D68">
         <v>96.764192139737986</v>
       </c>
-      <c r="M68">
+      <c r="E68">
         <v>76.553483807654558</v>
       </c>
-      <c r="N68">
+      <c r="F68">
         <v>-20.210708332083428</v>
       </c>
-      <c r="O68">
+      <c r="G68">
         <v>1019</v>
       </c>
-      <c r="P68" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="9:16">
-      <c r="I69">
+    <row r="69" spans="1:8">
+      <c r="A69">
         <v>15</v>
       </c>
-      <c r="J69">
+      <c r="B69">
         <v>5</v>
       </c>
-      <c r="K69" t="s">
+      <c r="C69" t="s">
         <v>11</v>
       </c>
-      <c r="L69">
+      <c r="D69">
         <v>70.908333333333331</v>
       </c>
-      <c r="M69">
+      <c r="E69">
         <v>82.906534325889169</v>
       </c>
-      <c r="N69">
+      <c r="F69">
         <v>11.998200992555837</v>
       </c>
-      <c r="O69">
+      <c r="G69">
         <v>1209</v>
       </c>
-      <c r="P69" s="1" t="s">
+      <c r="H69" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="9:16">
-      <c r="I70">
+    <row r="70" spans="1:8">
+      <c r="A70">
         <v>15</v>
       </c>
-      <c r="J70">
+      <c r="B70">
         <v>6</v>
       </c>
-      <c r="K70" t="s">
+      <c r="C70" t="s">
         <v>13</v>
       </c>
-      <c r="L70">
+      <c r="D70">
         <v>108.34297520661157</v>
       </c>
-      <c r="M70">
+      <c r="E70">
         <v>122.55608365019012</v>
       </c>
-      <c r="N70">
+      <c r="F70">
         <v>14.213108443578548</v>
       </c>
-      <c r="O70">
+      <c r="G70">
         <v>1052</v>
       </c>
-      <c r="P70" t="s">
+      <c r="H70" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="9:16">
-      <c r="I71">
+    <row r="71" spans="1:8">
+      <c r="A71">
         <v>15</v>
       </c>
-      <c r="J71">
+      <c r="B71">
         <v>7</v>
       </c>
-      <c r="K71" t="s">
+      <c r="C71" t="s">
         <v>1</v>
       </c>
-      <c r="L71">
+      <c r="D71">
         <v>78.987499999999997</v>
       </c>
-      <c r="M71">
+      <c r="E71">
         <v>85.48972884141331</v>
       </c>
-      <c r="N71">
+      <c r="F71">
         <v>6.5022288414133129</v>
       </c>
-      <c r="O71">
+      <c r="G71">
         <v>1217</v>
       </c>
-      <c r="P71" s="1" t="s">
+      <c r="H71" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="9:16">
-      <c r="I72">
+    <row r="72" spans="1:8">
+      <c r="A72">
         <v>15</v>
       </c>
-      <c r="J72">
+      <c r="B72">
         <v>8</v>
       </c>
-      <c r="K72" t="s">
+      <c r="C72" t="s">
         <v>53</v>
       </c>
-      <c r="L72">
+      <c r="D72">
         <v>70.174311926605498</v>
       </c>
-      <c r="M72">
+      <c r="E72">
         <v>71.870925684485002</v>
       </c>
-      <c r="N72">
+      <c r="F72">
         <v>1.6966137578795042</v>
       </c>
-      <c r="O72">
+      <c r="G72">
         <v>767</v>
       </c>
-      <c r="P72" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="9:16">
-      <c r="I73">
+    <row r="73" spans="1:8">
+      <c r="A73">
         <v>15</v>
       </c>
-      <c r="J73">
+      <c r="B73">
         <v>9</v>
       </c>
-      <c r="K73" t="s">
+      <c r="C73" t="s">
         <v>9</v>
       </c>
-      <c r="L73">
+      <c r="D73">
         <v>73.441025641025647</v>
       </c>
-      <c r="M73">
+      <c r="E73">
         <v>91.13448607108549</v>
       </c>
-      <c r="N73">
+      <c r="F73">
         <v>17.693460430059801</v>
       </c>
-      <c r="O73">
+      <c r="G73">
         <v>1041</v>
       </c>
-      <c r="P73" t="s">
+      <c r="H73" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="9:16">
-      <c r="I74">
+    <row r="74" spans="1:8">
+      <c r="A74">
         <v>15</v>
       </c>
-      <c r="J74">
+      <c r="B74">
         <v>10</v>
       </c>
-      <c r="K74" t="s">
+      <c r="C74" t="s">
         <v>2</v>
       </c>
-      <c r="L74">
+      <c r="D74">
         <v>70.239669421487605</v>
       </c>
-      <c r="M74">
+      <c r="E74">
         <v>79.065693430656935</v>
       </c>
-      <c r="N74">
+      <c r="F74">
         <v>8.8260240091693305</v>
       </c>
-      <c r="O74">
+      <c r="G74">
         <v>1096</v>
       </c>
-      <c r="P74" t="s">
+      <c r="H74" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3944,14 +4058,14 @@
       </c>
       <c r="D88" cm="1">
         <f t="array" ref="D88">AVERAGE(_xlfn._xlws.FILTER($D$1:D87, $C$1:C87=C88))</f>
-        <v>76.723668421052622</v>
+        <v>73.800565271132371</v>
       </c>
       <c r="E88" s="1">
         <v>88.738870000000006</v>
       </c>
       <c r="F88" s="1">
         <f>E88-D88</f>
-        <v>12.015201578947384</v>
+        <v>14.938304728867635</v>
       </c>
       <c r="G88" s="1">
         <v>988</v>
@@ -3972,14 +4086,14 @@
       </c>
       <c r="D89" cm="1">
         <f t="array" ref="D89">AVERAGE(_xlfn._xlws.FILTER($D$1:D88, $C$1:C88=C89))</f>
-        <v>79.035122330659533</v>
+        <v>78.131499225071849</v>
       </c>
       <c r="E89">
         <v>71.94111232279171</v>
       </c>
       <c r="F89" s="1">
         <f t="shared" ref="F89:F92" si="0">E89-D89</f>
-        <v>-7.0940100078678228</v>
+        <v>-6.1903869022801388</v>
       </c>
       <c r="G89">
         <v>917</v>
@@ -4000,14 +4114,14 @@
       </c>
       <c r="D90" cm="1">
         <f t="array" ref="D90">AVERAGE(_xlfn._xlws.FILTER($D$1:D89, $C$1:C89=C90))</f>
-        <v>70.350639825805658</v>
+        <v>71.84023868373572</v>
       </c>
       <c r="E90" s="1">
         <v>73.830389999999994</v>
       </c>
       <c r="F90" s="1">
         <f t="shared" si="0"/>
-        <v>3.4797501741943364</v>
+        <v>1.9901513162642743</v>
       </c>
       <c r="G90" s="1">
         <v>849</v>
